--- a/output/pdf_financials_xlsx/AGET.xlsx
+++ b/output/pdf_financials_xlsx/AGET.xlsx
@@ -2357,10 +2357,10 @@
         <v>0.013302</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.013302</v>
+        <v>0.013572</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.013302</v>
+        <v>0.013572</v>
       </c>
     </row>
     <row r="93">
@@ -4138,7 +4138,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4616,7 +4620,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AGET.xlsx
+++ b/output/pdf_financials_xlsx/AGET.xlsx
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.07513499999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.007581</v>
       </c>
     </row>
     <row r="13">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.672115</v>
+        <v>-5.74725</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.950371</v>
+        <v>-1.957952</v>
       </c>
     </row>
     <row r="28">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.604637</v>
+        <v>-5.679772</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.925323</v>
+        <v>-1.932904</v>
       </c>
     </row>
     <row r="30">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-319.5703168655106</v>
+        <v>-323.8544329925123</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-308.8636206860595</v>
+        <v>-310.0797777196694</v>
       </c>
     </row>
     <row r="31">
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.721422</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.519925</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.010253</v>
       </c>
     </row>
     <row r="35">
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.721422</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.519925</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.010253</v>
       </c>
     </row>
     <row r="37">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.80875</v>
+        <v>0.087328</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.614709</v>
+        <v>0.09478399999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.059502</v>
+        <v>0.049249</v>
       </c>
     </row>
     <row r="49">
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06079</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.028098</v>
       </c>
     </row>
     <row r="125">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06079</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.028098</v>
       </c>
     </row>
     <row r="126">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5428,7 +5428,11 @@
           <t>Receipt of sublease payments</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5618,7 +5622,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -6224,7 +6232,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6736,7 +6744,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7448,7 +7456,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">

--- a/output/pdf_financials_xlsx/AGET.xlsx
+++ b/output/pdf_financials_xlsx/AGET.xlsx
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.000761</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.026884</v>
       </c>
     </row>
     <row r="113">
@@ -4920,7 +4920,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AGET.xlsx
+++ b/output/pdf_financials_xlsx/AGET.xlsx
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.003959</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
         <v>0.683376</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.003959</v>
+        <v>0.007918</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
         <v>0.087328</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.09478399999999999</v>
+        <v>0.090825</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.049249</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03516</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03516</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.746395</v>
+        <v>-3.781555</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.481574</v>
@@ -5360,7 +5360,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
